--- a/data-manipulation-scripts/sheets-cleanup/sheets/RETOR BOMBA OLEO.xlsx
+++ b/data-manipulation-scripts/sheets-cleanup/sheets/RETOR BOMBA OLEO.xlsx
@@ -31,7 +31,7 @@
     <t>10765</t>
   </si>
   <si>
-    <t>RETOR BOMBA OLEO SOLIDEZ TITAN CG150/ XR190-300</t>
+    <t>ROTOR  BOMBA OLEO SOLIDEZ TITAN CG150/ XR190-300</t>
   </si>
   <si>
     <t>8413.30.30</t>
@@ -40,25 +40,25 @@
     <t>7899468062247</t>
   </si>
   <si>
-    <t>RETOR BOMBA OLEO AUDAX BROS NXR160/ TITAN FAN160/ XRE190</t>
+    <t>ROTOR  BOMBA OLEO AUDAX BROS NXR160/ TITAN FAN160/ XRE190</t>
   </si>
   <si>
     <t>7899468040498</t>
   </si>
   <si>
-    <t>RETOR BOMBA OLEO AUDAX TITAN150 2004 A 2015/ FAN125 2009 A 2018/FAN150 2010/ CRF150F 2012 A 2017/ NXR150 2006 A 2015</t>
+    <t>ROTOR  BOMBA OLEO AUDAX TITAN150 2004 A 2015/ FAN125 2009 A 2018/FAN150 2010/ CRF150F 2012 A 2017/ NXR150 2006 A 2015</t>
   </si>
   <si>
     <t>7908429131431</t>
   </si>
   <si>
-    <t>RETOR BOMBA OLEO EMBUS TITAN FAN150 2004 A 2015/ BROS NXR150 2006 A 2015 11064-E</t>
+    <t>ROTOR  BOMBA OLEO EMBUS TITAN FAN150 2004 A 2015/ BROS NXR150 2006 A 2015 11064-E</t>
   </si>
   <si>
     <t>7908073705673</t>
   </si>
   <si>
-    <t>RETOR BOMBA OLEO SMARTFOX TITAN/ NX/ XR</t>
+    <t>ROTOR  BOMBA OLEO SMARTFOX TITAN/ NX/ XR</t>
   </si>
 </sst>
 </file>
@@ -116,10 +116,10 @@
       <alignment horizontal="center" vertical="bottom"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" vertical="bottom"/>
+      <alignment horizontal="center" readingOrder="0" vertical="bottom"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment vertical="bottom"/>
+      <alignment horizontal="center" vertical="bottom"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" vertical="bottom"/>
@@ -392,10 +392,12 @@
       <c r="B2" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="C2" s="4">
+      <c r="C2" s="5">
         <v>2.0</v>
       </c>
-      <c r="D2" s="5"/>
+      <c r="D2" s="4">
+        <v>65.0</v>
+      </c>
       <c r="E2" s="6" t="s">
         <v>7</v>
       </c>
@@ -428,10 +430,10 @@
       <c r="B3" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="C3" s="4">
+      <c r="C3" s="5">
         <v>2.0</v>
       </c>
-      <c r="D3" s="4">
+      <c r="D3" s="5">
         <v>70.0</v>
       </c>
       <c r="E3" s="6" t="s">
@@ -466,10 +468,10 @@
       <c r="B4" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="C4" s="4">
+      <c r="C4" s="5">
         <v>1.0</v>
       </c>
-      <c r="D4" s="4">
+      <c r="D4" s="5">
         <v>70.0</v>
       </c>
       <c r="E4" s="6" t="s">
@@ -501,13 +503,15 @@
       <c r="A5" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="B5" s="8" t="s">
+      <c r="B5" s="4" t="s">
         <v>13</v>
       </c>
       <c r="C5" s="8">
         <v>2.0</v>
       </c>
-      <c r="D5" s="7"/>
+      <c r="D5" s="4">
+        <v>65.0</v>
+      </c>
       <c r="E5" s="6" t="s">
         <v>7</v>
       </c>
@@ -537,13 +541,15 @@
       <c r="A6" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="B6" s="8" t="s">
+      <c r="B6" s="4" t="s">
         <v>15</v>
       </c>
       <c r="C6" s="8">
         <v>10.0</v>
       </c>
-      <c r="D6" s="7"/>
+      <c r="D6" s="4">
+        <v>40.0</v>
+      </c>
       <c r="E6" s="6" t="s">
         <v>7</v>
       </c>
